--- a/static-route-missing-threshold/WarehouseDetail_records(static-route-missing-threshold).xlsx
+++ b/static-route-missing-threshold/WarehouseDetail_records(static-route-missing-threshold).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rndc/Desktop/Work related/Documents/order-no-desig/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rndc/Desktop/Work related/Documents/static-route-missing-threshold/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744EBD89-A137-2B49-AFB6-1E70D6515013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C5AB57-A894-3F49-A64C-75DBA55469CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34560" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF01000000}"/>
+    <workbookView xWindow="-38400" yWindow="740" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF01000000}"/>
   </bookViews>
   <sheets>
     <sheet name="(main group)" sheetId="6" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="184">
   <si>
     <t>Current</t>
   </si>
@@ -1509,6 +1509,132 @@
   </si>
   <si>
     <t>TBD</t>
+  </si>
+  <si>
+    <t>{
+    "alertName":"STATIC ROUTE MISSING THRESHOLD VALUE",
+    "dataSource":"MAWM",
+    "database":{
+        "connection":"MAPRD_NEW",
+        "type":"MySQL",
+        "uri":"jdbc:{host}:{port}/information_schema"
+    },
+    "email":{
+        "subject":"Splunk Alert: $alertName$",
+        "body":"&lt;pre&gt;The alert condition for ''$name$'' was triggered.&lt;br /&gt;&lt;br /&gt;***MSP TO CLEAN UP***&lt;br /&gt;Configure the necessary values in the Static Route UI&lt;/pre&gt;",
+        "fromEmail":"wms-tools-noreply@rndc-usa.com",
+        "toEmail":"Jonathan.Snell@RNDC-USA.COM, Preston.Mccauley@RNDC-USA.COM, Rob.Garcia@RNDC-USA.COM, Jordan.Stoll@rndc-usa.com, Richard.Gay@RNDC-USA.COM, Billy.Calloway@RNDC-USA.COM, Ryan.Black@rndc-usa.com",
+        "ccEmail":"wmsinternal@rndc-usa.com, wmsconsultant@rndc-usa.com, WMSMSPSupport@RNDC-USA.COM",
+        "footer":"",
+        "attachment":["link-to-alert","link-to-results", "inline-table"]
+    },
+    "sql":"SELECT Substr(profile_id, 1, 3) ''WHSE'', static_route_id, ext_threshold ''THRESHOLD_VALUE'' FROM default_routing.RTG_STATIC_ROUTE WHERE ext_threshold IS NULL AND profile_id = ''$orgId_Org_Profile'' "
+}'</t>
+  </si>
+  <si>
+    <t>{
+    "alertName":"STATIC ROUTE MISSING THRESHOLD VALUE",
+    "dataSource":"MAWM",
+    "database":{
+        "connection":"MAPRD_NEW",
+        "type":"MySQL",
+        "uri":"jdbc:{host}:{port}/information_schema"
+    },
+    "email":{
+        "subject":"Splunk Alert: $alertName$",
+        "body":"&lt;pre&gt;The alert condition for ''$name$'' was triggered.&lt;br /&gt;&lt;br /&gt;***MSP TO CLEAN UP***&lt;br /&gt;Configure the necessary values in the Static Route UI&lt;/pre&gt;",
+        "fromEmail":"wms-tools-noreply@rndc-usa.com",
+        "toEmail":"wmsinternal@RNDC-USA.COM, WMSMSPSupport@RNDC-USA.COM",
+        "ccEmail":"",
+        "footer":"",
+        "attachment":["link-to-alert","link-to-results", "inline-table"]
+    },
+    "sql":"SELECT Substr(profile_id, 1, 3) ''WHSE'', static_route_id, ext_threshold ''THRESHOLD_VALUE'' FROM default_routing.RTG_STATIC_ROUTE WHERE ext_threshold IS NULL AND profile_id = ''$orgId_Org_Profile'' "
+}'</t>
+  </si>
+  <si>
+    <t>{
+    "alertName":"STATIC ROUTE MISSING THRESHOLD VALUE",
+    "dataSource":"MAWM",
+    "database":{
+        "connection":"MAPRD_NEW",
+        "type":"MySQL",
+        "uri":"jdbc:{host}:{port}/information_schema"
+    },
+    "email":{
+        "subject":"Splunk Alert: $alertName$",
+        "body":"&lt;pre&gt;The alert condition for ''$name$'' was triggered.&lt;br /&gt;&lt;br /&gt;***MSP TO CLEAN UP***&lt;br /&gt;Configure the necessary values in the Static Route UI&lt;/pre&gt;",
+        "fromEmail":"wms-tools-noreply@rndc-usa.com",
+        "toEmail":"Travis.Eldridge@rndc-usa.com,joseph.duran@rndc-usa.com,travis.gusler@rndc-usa.com,christopher.gonzales@rndc-usa.com,Larry.Shelton@RNDC-USA.COM, Octavio.Chavez@RNDC-USA.COM, kameron.phipps@rndc-usa.com,",
+        "ccEmail":"wmsinternal@rndc-usa.com, wmsconsultant@rndc-usa.com, WMSMSPSupport@RNDC-USA.COM",
+        "footer":"",
+        "attachment":["link-to-alert","link-to-results", "inline-table"]
+    },
+    "sql":"SELECT Substr(profile_id, 1, 3) ''WHSE'', static_route_id, ext_threshold ''THRESHOLD_VALUE'' FROM default_routing.RTG_STATIC_ROUTE WHERE ext_threshold IS NULL AND profile_id = ''$orgId_Org_Profile'' "
+}'</t>
+  </si>
+  <si>
+    <t>{
+    "alertName":"STATIC ROUTE MISSING THRESHOLD VALUE",
+    "dataSource":"MAWM",
+    "database":{
+        "connection":"MAPRD_NEW",
+        "type":"MySQL",
+        "uri":"jdbc:{host}:{port}/information_schema"
+    },
+    "email":{
+        "subject":"Splunk Alert: $alertName$",
+        "body":"&lt;pre&gt;The alert condition for ''$name$'' was triggered.&lt;br /&gt;&lt;br /&gt;***MSP TO CLEAN UP***&lt;br /&gt;Configure the necessary values in the Static Route UI&lt;/pre&gt;",
+        "fromEmail":"wms-tools-noreply@rndc-usa.com",
+        "toEmail":"demetrius.dever@rndc-usa.com,Michael.Clark@RNDC-USA.com,clarence.hall@rndc-usa.com,brian.bowen@rndc-usa.com,barbara.jackson@rndc-usa.com,rodney.williams@rndc-usa.com",
+        "ccEmail":"wmsinternal@rndc-usa.com, wmsconsultant@rndc-usa.com, WMSMSPSupport@RNDC-USA.COM",
+        "footer":"",
+        "attachment":["link-to-alert","link-to-results", "inline-table"]
+    },
+    "sql":"SELECT Substr(profile_id, 1, 3) ''WHSE'', static_route_id, ext_threshold ''THRESHOLD_VALUE'' FROM default_routing.RTG_STATIC_ROUTE WHERE ext_threshold IS NULL AND profile_id = ''$orgId_Org_Profile'' "
+}'</t>
+  </si>
+  <si>
+    <t>{
+    "alertName":"STATIC ROUTE MISSING THRESHOLD VALUE",
+    "dataSource":"MAWM",
+    "database":{
+        "connection":"MAPRD_NEW",
+        "type":"MySQL",
+        "uri":"jdbc:{host}:{port}/information_schema"
+    },
+    "email":{
+        "subject":"Splunk Alert: $alertName$",
+        "body":"&lt;pre&gt;The alert condition for ''$name$'' was triggered.&lt;/pre&gt;",
+        "fromEmail":"wms-tools-noreply@rndc-usa.com",
+        "toEmail":"Ryan.Metz@rndc-usa.com, John.Hall@rndc-usa.com, Anthony.Coleman@rndc-usa.com, Dazzle.Keyser@rndc-usa.com, Douglas.Garner@rndc-usa.com",
+        "ccEmail":"wmsinternal@rndc-usa.com, wmsconsultant@rndc-usa.com, WMSMSPSupport@RNDC-USA.COM",
+        "footer":"",
+        "attachment":["link-to-alert","link-to-results", "inline-table"]
+    },
+    "sql":"SELECT Substr(profile_id, 1, 3) ''WHSE'', static_route_id, ext_threshold ''THRESHOLD_VALUE'' FROM default_routing.RTG_STATIC_ROUTE WHERE ext_threshold IS NULL AND profile_id = ''$orgId_Org_Profile'' "
+}'</t>
+  </si>
+  <si>
+    <t>{
+    "alertName":"STATIC ROUTE MISSING THRESHOLD VALUE",
+    "dataSource":"MAWM",
+    "database":{
+        "connection":"MAPRD_NEW",
+        "type":"MySQL",
+        "uri":"jdbc:{host}:{port}/information_schema"
+    },
+    "email":{
+        "subject":"Splunk Alert: $alertName$",
+        "body":"&lt;pre&gt;The alert condition for ''$name$'' was triggered.&lt;/pre&gt;",
+        "fromEmail":"wms-tools-noreply@rndc-usa.com",
+        "toEmail":"wmsinternal@RNDC-USA.COM, WMSMSPSupport@RNDC-USA.COM",
+        "ccEmail":"",
+        "footer":"",
+        "attachment":["link-to-alert","link-to-results", "inline-table"]
+    },
+    "sql":"SELECT Substr(profile_id, 1, 3) ''WHSE'', static_route_id, ext_threshold ''THRESHOLD_VALUE'' FROM default_routing.RTG_STATIC_ROUTE WHERE ext_threshold IS NULL AND profile_id = ''$orgId_Org_Profile'' "
+}'</t>
   </si>
 </sst>
 </file>
@@ -1594,7 +1720,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1625,6 +1751,8 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1963,7 +2091,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10.1640625" customWidth="1"/>
-    <col min="7" max="7" width="80.83203125" customWidth="1"/>
+    <col min="7" max="7" width="80.83203125" style="14" customWidth="1"/>
     <col min="8" max="8" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1986,7 +2114,7 @@
       <c r="F1" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="14" t="s">
         <v>167</v>
       </c>
       <c r="H1" s="3" t="s">
@@ -2021,8 +2149,8 @@
       <c r="F2" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G2" t="s">
-        <v>122</v>
+      <c r="G2" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>172</v>
@@ -2057,8 +2185,8 @@
       <c r="F3" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G3" t="s">
-        <v>147</v>
+      <c r="G3" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>172</v>
@@ -2092,8 +2220,8 @@
       <c r="F4" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G4" t="s">
-        <v>123</v>
+      <c r="G4" s="15" t="s">
+        <v>178</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>172</v>
@@ -2128,8 +2256,8 @@
       <c r="F5" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G5" t="s">
-        <v>124</v>
+      <c r="G5" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>172</v>
@@ -2163,8 +2291,8 @@
       <c r="F6" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G6" t="s">
-        <v>148</v>
+      <c r="G6" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>172</v>
@@ -2198,8 +2326,8 @@
       <c r="F7" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G7" t="s">
-        <v>159</v>
+      <c r="G7" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>172</v>
@@ -2233,8 +2361,8 @@
       <c r="F8" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G8" t="s">
-        <v>160</v>
+      <c r="G8" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>172</v>
@@ -2268,8 +2396,8 @@
       <c r="F9" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G9" t="s">
-        <v>161</v>
+      <c r="G9" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>172</v>
@@ -2303,8 +2431,8 @@
       <c r="F10" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G10" t="s">
-        <v>125</v>
+      <c r="G10" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>172</v>
@@ -2338,8 +2466,8 @@
       <c r="F11" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G11" t="s">
-        <v>126</v>
+      <c r="G11" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>172</v>
@@ -2373,8 +2501,8 @@
       <c r="F12" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G12" t="s">
-        <v>127</v>
+      <c r="G12" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>172</v>
@@ -2408,8 +2536,8 @@
       <c r="F13" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G13" t="s">
-        <v>128</v>
+      <c r="G13" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>172</v>
@@ -2443,8 +2571,8 @@
       <c r="F14" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G14" t="s">
-        <v>129</v>
+      <c r="G14" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>172</v>
@@ -2478,8 +2606,8 @@
       <c r="F15" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G15" t="s">
-        <v>130</v>
+      <c r="G15" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>172</v>
@@ -2513,8 +2641,8 @@
       <c r="F16" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G16" t="s">
-        <v>156</v>
+      <c r="G16" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>172</v>
@@ -2548,8 +2676,8 @@
       <c r="F17" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G17" t="s">
-        <v>131</v>
+      <c r="G17" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>172</v>
@@ -2583,8 +2711,8 @@
       <c r="F18" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G18" t="s">
-        <v>132</v>
+      <c r="G18" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>172</v>
@@ -2618,8 +2746,8 @@
       <c r="F19" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G19" t="s">
-        <v>133</v>
+      <c r="G19" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>172</v>
@@ -2653,8 +2781,8 @@
       <c r="F20" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G20" t="s">
-        <v>134</v>
+      <c r="G20" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>172</v>
@@ -2688,8 +2816,8 @@
       <c r="F21" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G21" t="s">
-        <v>153</v>
+      <c r="G21" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>172</v>
@@ -2723,8 +2851,8 @@
       <c r="F22" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G22" t="s">
-        <v>155</v>
+      <c r="G22" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>172</v>
@@ -2758,8 +2886,8 @@
       <c r="F23" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G23" t="s">
-        <v>135</v>
+      <c r="G23" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>172</v>
@@ -2793,8 +2921,8 @@
       <c r="F24" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G24" t="s">
-        <v>136</v>
+      <c r="G24" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>172</v>
@@ -2828,8 +2956,8 @@
       <c r="F25" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G25" t="s">
-        <v>149</v>
+      <c r="G25" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>172</v>
@@ -2863,8 +2991,8 @@
       <c r="F26" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G26" t="s">
-        <v>150</v>
+      <c r="G26" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>172</v>
@@ -2898,8 +3026,8 @@
       <c r="F27" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G27" t="s">
-        <v>154</v>
+      <c r="G27" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>172</v>
@@ -2933,8 +3061,8 @@
       <c r="F28" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G28" t="s">
-        <v>137</v>
+      <c r="G28" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>172</v>
@@ -2968,8 +3096,8 @@
       <c r="F29" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G29" t="s">
-        <v>152</v>
+      <c r="G29" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>172</v>
@@ -3003,8 +3131,8 @@
       <c r="F30" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G30" t="s">
-        <v>138</v>
+      <c r="G30" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>172</v>
@@ -3038,8 +3166,8 @@
       <c r="F31" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G31" t="s">
-        <v>139</v>
+      <c r="G31" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>172</v>
@@ -3073,8 +3201,8 @@
       <c r="F32" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G32" t="s">
-        <v>140</v>
+      <c r="G32" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>172</v>
@@ -3108,8 +3236,8 @@
       <c r="F33" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G33" t="s">
-        <v>141</v>
+      <c r="G33" s="15" t="s">
+        <v>182</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>172</v>
@@ -3143,8 +3271,8 @@
       <c r="F34" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G34" t="s">
-        <v>162</v>
+      <c r="G34" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>172</v>
@@ -3178,8 +3306,8 @@
       <c r="F35" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G35" t="s">
-        <v>142</v>
+      <c r="G35" s="15" t="s">
+        <v>179</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>172</v>
@@ -3213,8 +3341,8 @@
       <c r="F36" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G36" t="s">
-        <v>121</v>
+      <c r="G36" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>172</v>
@@ -3248,8 +3376,8 @@
       <c r="F37" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G37" t="s">
-        <v>157</v>
+      <c r="G37" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>172</v>
@@ -3283,8 +3411,8 @@
       <c r="F38" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G38" t="s">
-        <v>151</v>
+      <c r="G38" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>172</v>
@@ -3318,8 +3446,8 @@
       <c r="F39" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G39" t="s">
-        <v>143</v>
+      <c r="G39" s="15" t="s">
+        <v>180</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>172</v>
@@ -3353,8 +3481,8 @@
       <c r="F40" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G40" t="s">
-        <v>144</v>
+      <c r="G40" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>172</v>
@@ -3388,8 +3516,8 @@
       <c r="F41" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G41" t="s">
-        <v>145</v>
+      <c r="G41" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>172</v>
@@ -3423,8 +3551,8 @@
       <c r="F42" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G42" t="s">
-        <v>163</v>
+      <c r="G42" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>172</v>
@@ -3458,8 +3586,8 @@
       <c r="F43" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G43" t="s">
-        <v>158</v>
+      <c r="G43" s="15" t="s">
+        <v>183</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>172</v>
@@ -3493,8 +3621,8 @@
       <c r="F44" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="G44" t="s">
-        <v>146</v>
+      <c r="G44" s="15" t="s">
+        <v>181</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>172</v>
